--- a/data/nzd0111/nzd0111.xlsx
+++ b/data/nzd0111/nzd0111.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H414"/>
+  <dimension ref="A1:H415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12850,6 +12850,36 @@
         <v>385.73</v>
       </c>
       <c r="H414" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>396.47</v>
+      </c>
+      <c r="C415" t="n">
+        <v>378.93</v>
+      </c>
+      <c r="D415" t="n">
+        <v>375.49</v>
+      </c>
+      <c r="E415" t="n">
+        <v>383.31</v>
+      </c>
+      <c r="F415" t="n">
+        <v>374.35</v>
+      </c>
+      <c r="G415" t="n">
+        <v>384.2</v>
+      </c>
+      <c r="H415" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12866,7 +12896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B564"/>
+  <dimension ref="A1:B565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18509,6 +18539,16 @@
       </c>
       <c r="B564" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>
@@ -18677,28 +18717,28 @@
         <v>0.053</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1119957154077632</v>
+        <v>0.1106678423780078</v>
       </c>
       <c r="J2" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K2" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02084363762918118</v>
+        <v>0.0204698691193137</v>
       </c>
       <c r="M2" t="n">
-        <v>4.00854033517959</v>
+        <v>4.003910897940788</v>
       </c>
       <c r="N2" t="n">
-        <v>31.74231153854555</v>
+        <v>31.68140832982123</v>
       </c>
       <c r="O2" t="n">
-        <v>5.63403155285321</v>
+        <v>5.628624017450555</v>
       </c>
       <c r="P2" t="n">
-        <v>396.1187762470308</v>
+        <v>396.1322267987519</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18755,28 +18795,28 @@
         <v>0.0517</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1734569384495487</v>
+        <v>0.1690740025635269</v>
       </c>
       <c r="J3" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K3" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06969710400005036</v>
+        <v>0.06631081484050749</v>
       </c>
       <c r="M3" t="n">
-        <v>3.387932869412597</v>
+        <v>3.400094173193512</v>
       </c>
       <c r="N3" t="n">
-        <v>21.73192407428431</v>
+        <v>21.85640873017559</v>
       </c>
       <c r="O3" t="n">
-        <v>4.661751181078234</v>
+        <v>4.67508382065772</v>
       </c>
       <c r="P3" t="n">
-        <v>382.9624998309147</v>
+        <v>383.0066933582836</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18833,28 +18873,28 @@
         <v>0.0497</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2249522866017187</v>
+        <v>0.2189826667722246</v>
       </c>
       <c r="J4" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K4" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1226849387437505</v>
+        <v>0.1159014595089423</v>
       </c>
       <c r="M4" t="n">
-        <v>3.377967479904332</v>
+        <v>3.394254594697956</v>
       </c>
       <c r="N4" t="n">
-        <v>19.58169782805962</v>
+        <v>19.86270630880308</v>
       </c>
       <c r="O4" t="n">
-        <v>4.42512122184914</v>
+        <v>4.456759619813826</v>
       </c>
       <c r="P4" t="n">
-        <v>381.2843907856893</v>
+        <v>381.3445829865743</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18911,28 +18951,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07667007659241591</v>
+        <v>0.07447970027019296</v>
       </c>
       <c r="J5" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K5" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01590961118515544</v>
+        <v>0.01508080846497128</v>
       </c>
       <c r="M5" t="n">
-        <v>3.440119203751382</v>
+        <v>3.440400817865166</v>
       </c>
       <c r="N5" t="n">
-        <v>19.67580021313514</v>
+        <v>19.67247436495017</v>
       </c>
       <c r="O5" t="n">
-        <v>4.435741224771249</v>
+        <v>4.435366316884116</v>
       </c>
       <c r="P5" t="n">
-        <v>385.5903525917429</v>
+        <v>385.6124383485191</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18989,28 +19029,28 @@
         <v>0.0648</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002274453043425043</v>
+        <v>-0.0009469740040397248</v>
       </c>
       <c r="J6" t="n">
+        <v>414</v>
+      </c>
+      <c r="K6" t="n">
         <v>413</v>
       </c>
-      <c r="K6" t="n">
-        <v>412</v>
-      </c>
       <c r="L6" t="n">
-        <v>1.069437042622301e-05</v>
+        <v>1.858044711977591e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>4.023021496702309</v>
+        <v>4.02673314236699</v>
       </c>
       <c r="N6" t="n">
-        <v>26.02895308750159</v>
+        <v>26.06077258089363</v>
       </c>
       <c r="O6" t="n">
-        <v>5.101857807456181</v>
+        <v>5.104975277206896</v>
       </c>
       <c r="P6" t="n">
-        <v>380.5724207242708</v>
+        <v>380.6050495486907</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19067,28 +19107,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02364315707925115</v>
+        <v>0.02418037506072883</v>
       </c>
       <c r="J7" t="n">
+        <v>414</v>
+      </c>
+      <c r="K7" t="n">
         <v>413</v>
       </c>
-      <c r="K7" t="n">
-        <v>412</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.0009945658985651695</v>
+        <v>0.001046276734628426</v>
       </c>
       <c r="M7" t="n">
-        <v>4.475878196884918</v>
+        <v>4.467348258188997</v>
       </c>
       <c r="N7" t="n">
-        <v>30.21397318001511</v>
+        <v>30.143453481487</v>
       </c>
       <c r="O7" t="n">
-        <v>5.496723858810365</v>
+        <v>5.490305408762522</v>
       </c>
       <c r="P7" t="n">
-        <v>382.5282942643727</v>
+        <v>382.522852951894</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19126,7 +19166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H414"/>
+  <dimension ref="A1:H415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36501,6 +36541,48 @@
         </is>
       </c>
     </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>-36.04788611773611,174.56477941723287</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>-36.04817913619416,174.56562546336843</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>-36.04833895358606,174.56649710449045</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>-36.048357203076726,174.567382249757</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>-36.048458018488795,174.56825906485744</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>-36.04831457849485,174.56913454636543</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0111/nzd0111.xlsx
+++ b/data/nzd0111/nzd0111.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H415"/>
+  <dimension ref="A1:H417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12880,6 +12880,66 @@
         <v>384.2</v>
       </c>
       <c r="H415" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>398.6</v>
+      </c>
+      <c r="C416" t="n">
+        <v>379.47</v>
+      </c>
+      <c r="D416" t="n">
+        <v>375.18</v>
+      </c>
+      <c r="E416" t="n">
+        <v>381.68</v>
+      </c>
+      <c r="F416" t="n">
+        <v>372.44</v>
+      </c>
+      <c r="G416" t="n">
+        <v>374.79</v>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:12:07+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>397.88</v>
+      </c>
+      <c r="C417" t="n">
+        <v>379.25</v>
+      </c>
+      <c r="D417" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="E417" t="n">
+        <v>380.04</v>
+      </c>
+      <c r="F417" t="n">
+        <v>372.3</v>
+      </c>
+      <c r="G417" t="n">
+        <v>373.6</v>
+      </c>
+      <c r="H417" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12896,7 +12956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B565"/>
+  <dimension ref="A1:B568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18549,6 +18609,36 @@
       </c>
       <c r="B565" t="n">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>0.72</v>
       </c>
     </row>
   </sheetData>
@@ -18717,28 +18807,28 @@
         <v>0.053</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1106678423780078</v>
+        <v>0.1098413669138456</v>
       </c>
       <c r="J2" t="n">
+        <v>416</v>
+      </c>
+      <c r="K2" t="n">
         <v>414</v>
       </c>
-      <c r="K2" t="n">
-        <v>412</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0204698691193137</v>
+        <v>0.02040378568528445</v>
       </c>
       <c r="M2" t="n">
-        <v>4.003910897940788</v>
+        <v>3.98768794116912</v>
       </c>
       <c r="N2" t="n">
-        <v>31.68140832982123</v>
+        <v>31.53212441593897</v>
       </c>
       <c r="O2" t="n">
-        <v>5.628624017450555</v>
+        <v>5.61534722131579</v>
       </c>
       <c r="P2" t="n">
-        <v>396.1322267987519</v>
+        <v>396.1406390141817</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18795,28 +18885,28 @@
         <v>0.0517</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1690740025635269</v>
+        <v>0.1608600518318282</v>
       </c>
       <c r="J3" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K3" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06631081484050749</v>
+        <v>0.06026706178413055</v>
       </c>
       <c r="M3" t="n">
-        <v>3.400094173193512</v>
+        <v>3.421653783169124</v>
       </c>
       <c r="N3" t="n">
-        <v>21.85640873017559</v>
+        <v>22.06249520542859</v>
       </c>
       <c r="O3" t="n">
-        <v>4.67508382065772</v>
+        <v>4.697073046635381</v>
       </c>
       <c r="P3" t="n">
-        <v>383.0066933582836</v>
+        <v>383.0898845953295</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18873,28 +18963,28 @@
         <v>0.0497</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2189826667722246</v>
+        <v>0.2062401218842891</v>
       </c>
       <c r="J4" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K4" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1159014595089423</v>
+        <v>0.1018156527583158</v>
       </c>
       <c r="M4" t="n">
-        <v>3.394254594697956</v>
+        <v>3.430614308936034</v>
       </c>
       <c r="N4" t="n">
-        <v>19.86270630880308</v>
+        <v>20.51781146032737</v>
       </c>
       <c r="O4" t="n">
-        <v>4.456759619813826</v>
+        <v>4.529659088753521</v>
       </c>
       <c r="P4" t="n">
-        <v>381.3445829865743</v>
+        <v>381.4736442723593</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18951,28 +19041,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07447970027019296</v>
+        <v>0.06767508157075139</v>
       </c>
       <c r="J5" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K5" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01508080846497128</v>
+        <v>0.01249354142949244</v>
       </c>
       <c r="M5" t="n">
-        <v>3.440400817865166</v>
+        <v>3.450573218970138</v>
       </c>
       <c r="N5" t="n">
-        <v>19.67247436495017</v>
+        <v>19.7945552476843</v>
       </c>
       <c r="O5" t="n">
-        <v>4.435366316884116</v>
+        <v>4.449107241647958</v>
       </c>
       <c r="P5" t="n">
-        <v>385.6124383485191</v>
+        <v>385.6813624458224</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19029,28 +19119,28 @@
         <v>0.0648</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0009469740040397248</v>
+        <v>-0.00930495816589629</v>
       </c>
       <c r="J6" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K6" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L6" t="n">
-        <v>1.858044711977591e-06</v>
+        <v>0.000179285498014492</v>
       </c>
       <c r="M6" t="n">
-        <v>4.02673314236699</v>
+        <v>4.043044565681175</v>
       </c>
       <c r="N6" t="n">
-        <v>26.06077258089363</v>
+        <v>26.25474453217947</v>
       </c>
       <c r="O6" t="n">
-        <v>5.104975277206896</v>
+        <v>5.123938380989712</v>
       </c>
       <c r="P6" t="n">
-        <v>380.6050495486907</v>
+        <v>380.6900802104249</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19107,28 +19197,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02418037506072883</v>
+        <v>0.01504915660835022</v>
       </c>
       <c r="J7" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K7" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001046276734628426</v>
+        <v>0.000405177315702332</v>
       </c>
       <c r="M7" t="n">
-        <v>4.467348258188997</v>
+        <v>4.492217636478653</v>
       </c>
       <c r="N7" t="n">
-        <v>30.143453481487</v>
+        <v>30.38121772617787</v>
       </c>
       <c r="O7" t="n">
-        <v>5.490305408762522</v>
+        <v>5.511915975972227</v>
       </c>
       <c r="P7" t="n">
-        <v>382.522852951894</v>
+        <v>382.6157549998946</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19166,7 +19256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H415"/>
+  <dimension ref="A1:H417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36583,6 +36673,90 @@
         </is>
       </c>
     </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>-36.04786723043118,174.56478366069902</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>-36.04817434319622,174.56562650718047</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>-36.04834171997322,174.56649661992557</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>-36.048371864317595,174.56738107473288</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>-36.04847522389316,174.5682598112963</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>-36.048399071753984,174.56914368372304</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:12:07+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>-36.0478736148723,174.56478222628812</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>-36.04817629589908,174.56562608192374</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>-36.04835314247502,174.5664946191412</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>-36.04838661550469,174.5673798924997</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>-36.048476485022285,174.5682598660091</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>-36.04840975687373,174.56914483924598</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0111/nzd0111.xlsx
+++ b/data/nzd0111/nzd0111.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H417"/>
+  <dimension ref="A1:H418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12942,6 +12942,36 @@
       <c r="H417" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>400.99</v>
+      </c>
+      <c r="C418" t="n">
+        <v>381.74</v>
+      </c>
+      <c r="D418" t="n">
+        <v>376.83</v>
+      </c>
+      <c r="E418" t="n">
+        <v>380.01</v>
+      </c>
+      <c r="F418" t="n">
+        <v>375.41</v>
+      </c>
+      <c r="G418" t="n">
+        <v>373.13</v>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12956,7 +12986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B568"/>
+  <dimension ref="A1:B569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18639,6 +18669,16 @@
       </c>
       <c r="B568" t="n">
         <v>0.72</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>1.01</v>
       </c>
     </row>
   </sheetData>
@@ -18807,28 +18847,28 @@
         <v>0.053</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1098413669138456</v>
+        <v>0.1108322654998929</v>
       </c>
       <c r="J2" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K2" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02040378568528445</v>
+        <v>0.02088224070162537</v>
       </c>
       <c r="M2" t="n">
-        <v>3.98768794116912</v>
+        <v>3.983650538186037</v>
       </c>
       <c r="N2" t="n">
-        <v>31.53212441593897</v>
+        <v>31.46507242658497</v>
       </c>
       <c r="O2" t="n">
-        <v>5.61534722131579</v>
+        <v>5.609373621589577</v>
       </c>
       <c r="P2" t="n">
-        <v>396.1406390141817</v>
+        <v>396.1304865549521</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18885,28 +18925,28 @@
         <v>0.0517</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1608600518318282</v>
+        <v>0.1579918181076453</v>
       </c>
       <c r="J3" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K3" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06026706178413055</v>
+        <v>0.05840188465189144</v>
       </c>
       <c r="M3" t="n">
-        <v>3.421653783169124</v>
+        <v>3.426724161418786</v>
       </c>
       <c r="N3" t="n">
-        <v>22.06249520542859</v>
+        <v>22.08488380780204</v>
       </c>
       <c r="O3" t="n">
-        <v>4.697073046635381</v>
+        <v>4.69945569271613</v>
       </c>
       <c r="P3" t="n">
-        <v>383.0898845953295</v>
+        <v>383.1191378882894</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18963,28 +19003,28 @@
         <v>0.0497</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2062401218842891</v>
+        <v>0.2010792464051232</v>
       </c>
       <c r="J4" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K4" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1018156527583158</v>
+        <v>0.09675978149269637</v>
       </c>
       <c r="M4" t="n">
-        <v>3.430614308936034</v>
+        <v>3.443956449035458</v>
       </c>
       <c r="N4" t="n">
-        <v>20.51781146032737</v>
+        <v>20.71238417168342</v>
       </c>
       <c r="O4" t="n">
-        <v>4.529659088753521</v>
+        <v>4.551086043098221</v>
       </c>
       <c r="P4" t="n">
-        <v>381.4736442723593</v>
+        <v>381.5262803602237</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19041,28 +19081,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06767508157075139</v>
+        <v>0.06386942180298562</v>
       </c>
       <c r="J5" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K5" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01249354142949244</v>
+        <v>0.01113528807631026</v>
       </c>
       <c r="M5" t="n">
-        <v>3.450573218970138</v>
+        <v>3.45731071923536</v>
       </c>
       <c r="N5" t="n">
-        <v>19.7945552476843</v>
+        <v>19.87964378110577</v>
       </c>
       <c r="O5" t="n">
-        <v>4.449107241647958</v>
+        <v>4.458659415239716</v>
       </c>
       <c r="P5" t="n">
-        <v>385.6813624458224</v>
+        <v>385.7201766049175</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19119,28 +19159,28 @@
         <v>0.0648</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.00930495816589629</v>
+        <v>-0.011884615361369</v>
       </c>
       <c r="J6" t="n">
+        <v>417</v>
+      </c>
+      <c r="K6" t="n">
         <v>416</v>
       </c>
-      <c r="K6" t="n">
-        <v>415</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.000179285498014492</v>
+        <v>0.0002935207099100667</v>
       </c>
       <c r="M6" t="n">
-        <v>4.043044565681175</v>
+        <v>4.044331266845556</v>
       </c>
       <c r="N6" t="n">
-        <v>26.25474453217947</v>
+        <v>26.25205166484034</v>
       </c>
       <c r="O6" t="n">
-        <v>5.123938380989712</v>
+        <v>5.123675601054416</v>
       </c>
       <c r="P6" t="n">
-        <v>380.6900802104249</v>
+        <v>380.7165079242568</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19197,28 +19237,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01504915660835022</v>
+        <v>0.009985564514308123</v>
       </c>
       <c r="J7" t="n">
+        <v>417</v>
+      </c>
+      <c r="K7" t="n">
         <v>416</v>
       </c>
-      <c r="K7" t="n">
-        <v>415</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.000405177315702332</v>
+        <v>0.0001781329038044177</v>
       </c>
       <c r="M7" t="n">
-        <v>4.492217636478653</v>
+        <v>4.506868103723795</v>
       </c>
       <c r="N7" t="n">
-        <v>30.38121772617787</v>
+        <v>30.54097929390817</v>
       </c>
       <c r="O7" t="n">
-        <v>5.511915975972227</v>
+        <v>5.526389354172231</v>
       </c>
       <c r="P7" t="n">
-        <v>382.6157549998946</v>
+        <v>382.6676297850629</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19256,7 +19296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H417"/>
+  <dimension ref="A1:H418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36757,6 +36797,48 @@
         </is>
       </c>
     </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>-36.04784603763344,174.56478842214474</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>-36.048154194852955,174.56563089505576</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>-36.04832699565444,174.56649919906093</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>-36.04838688534346,174.56737987087348</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>-36.04844846993973,174.56825865060367</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>-36.04841397704707,174.56914529562908</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0111/nzd0111.xlsx
+++ b/data/nzd0111/nzd0111.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H418"/>
+  <dimension ref="A1:H423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12972,6 +12972,156 @@
       <c r="H418" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>401.29</v>
+      </c>
+      <c r="C419" t="n">
+        <v>386.43</v>
+      </c>
+      <c r="D419" t="n">
+        <v>379.65</v>
+      </c>
+      <c r="E419" t="n">
+        <v>380.49</v>
+      </c>
+      <c r="F419" t="n">
+        <v>376.62</v>
+      </c>
+      <c r="G419" t="n">
+        <v>374.77</v>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>399.57</v>
+      </c>
+      <c r="C420" t="n">
+        <v>384.55</v>
+      </c>
+      <c r="D420" t="n">
+        <v>379.4</v>
+      </c>
+      <c r="E420" t="n">
+        <v>380.65</v>
+      </c>
+      <c r="F420" t="n">
+        <v>375.31</v>
+      </c>
+      <c r="G420" t="n">
+        <v>374.82</v>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:05+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>399.57</v>
+      </c>
+      <c r="C421" t="n">
+        <v>384.55</v>
+      </c>
+      <c r="D421" t="n">
+        <v>379.52</v>
+      </c>
+      <c r="E421" t="n">
+        <v>380.97</v>
+      </c>
+      <c r="F421" t="n">
+        <v>374.94</v>
+      </c>
+      <c r="G421" t="n">
+        <v>375.37</v>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>398.07</v>
+      </c>
+      <c r="C422" t="n">
+        <v>384.67</v>
+      </c>
+      <c r="D422" t="n">
+        <v>379.32</v>
+      </c>
+      <c r="E422" t="n">
+        <v>379.14</v>
+      </c>
+      <c r="F422" t="n">
+        <v>374.31</v>
+      </c>
+      <c r="G422" t="n">
+        <v>374.52</v>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>397.27</v>
+      </c>
+      <c r="C423" t="n">
+        <v>383.59</v>
+      </c>
+      <c r="D423" t="n">
+        <v>379.71</v>
+      </c>
+      <c r="E423" t="n">
+        <v>379.71</v>
+      </c>
+      <c r="F423" t="n">
+        <v>374.34</v>
+      </c>
+      <c r="G423" t="n">
+        <v>374.88</v>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12986,7 +13136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B569"/>
+  <dimension ref="A1:B574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18679,6 +18829,56 @@
       </c>
       <c r="B569" t="n">
         <v>1.01</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>-0.15</v>
       </c>
     </row>
   </sheetData>
@@ -18847,28 +19047,28 @@
         <v>0.053</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1108322654998929</v>
+        <v>0.1109920853137151</v>
       </c>
       <c r="J2" t="n">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="K2" t="n">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02088224070162537</v>
+        <v>0.02154107547049966</v>
       </c>
       <c r="M2" t="n">
-        <v>3.983650538186037</v>
+        <v>3.950691101398388</v>
       </c>
       <c r="N2" t="n">
-        <v>31.46507242658497</v>
+        <v>31.11352007400109</v>
       </c>
       <c r="O2" t="n">
-        <v>5.609373621589577</v>
+        <v>5.577949450649503</v>
       </c>
       <c r="P2" t="n">
-        <v>396.1304865549521</v>
+        <v>396.1288726933631</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18925,28 +19125,28 @@
         <v>0.0517</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1579918181076453</v>
+        <v>0.1516225914475232</v>
       </c>
       <c r="J3" t="n">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="K3" t="n">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05840188465189144</v>
+        <v>0.05536217295712675</v>
       </c>
       <c r="M3" t="n">
-        <v>3.426724161418786</v>
+        <v>3.415200960572585</v>
       </c>
       <c r="N3" t="n">
-        <v>22.08488380780204</v>
+        <v>21.90880999907227</v>
       </c>
       <c r="O3" t="n">
-        <v>4.69945569271613</v>
+        <v>4.680684778862199</v>
       </c>
       <c r="P3" t="n">
-        <v>383.1191378882894</v>
+        <v>383.1844186344237</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19003,28 +19203,28 @@
         <v>0.0497</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2010792464051232</v>
+        <v>0.1828704773812529</v>
       </c>
       <c r="J4" t="n">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="K4" t="n">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09675978149269637</v>
+        <v>0.08137507950269873</v>
       </c>
       <c r="M4" t="n">
-        <v>3.443956449035458</v>
+        <v>3.48148118357086</v>
       </c>
       <c r="N4" t="n">
-        <v>20.71238417168342</v>
+        <v>21.08495839134615</v>
       </c>
       <c r="O4" t="n">
-        <v>4.551086043098221</v>
+        <v>4.591836058849026</v>
       </c>
       <c r="P4" t="n">
-        <v>381.5262803602237</v>
+        <v>381.7128564204488</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19081,28 +19281,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06386942180298562</v>
+        <v>0.04600223358216609</v>
       </c>
       <c r="J5" t="n">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="K5" t="n">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01113528807631026</v>
+        <v>0.005804575934685752</v>
       </c>
       <c r="M5" t="n">
-        <v>3.45731071923536</v>
+        <v>3.487944943437795</v>
       </c>
       <c r="N5" t="n">
-        <v>19.87964378110577</v>
+        <v>20.24407113933147</v>
       </c>
       <c r="O5" t="n">
-        <v>4.458659415239716</v>
+        <v>4.499341189477796</v>
       </c>
       <c r="P5" t="n">
-        <v>385.7201766049175</v>
+        <v>385.9032627191947</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19159,28 +19359,28 @@
         <v>0.0648</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.011884615361369</v>
+        <v>-0.0250358000842579</v>
       </c>
       <c r="J6" t="n">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="K6" t="n">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002935207099100667</v>
+        <v>0.001323567221282462</v>
       </c>
       <c r="M6" t="n">
-        <v>4.044331266845556</v>
+        <v>4.053688506839947</v>
       </c>
       <c r="N6" t="n">
-        <v>26.25205166484034</v>
+        <v>26.26825562879246</v>
       </c>
       <c r="O6" t="n">
-        <v>5.123675601054416</v>
+        <v>5.125256640285681</v>
       </c>
       <c r="P6" t="n">
-        <v>380.7165079242568</v>
+        <v>380.8518785081047</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19237,28 +19437,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009985564514308123</v>
+        <v>-0.01003365269954293</v>
       </c>
       <c r="J7" t="n">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="K7" t="n">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001781329038044177</v>
+        <v>0.0001808135766265817</v>
       </c>
       <c r="M7" t="n">
-        <v>4.506868103723795</v>
+        <v>4.552958279513748</v>
       </c>
       <c r="N7" t="n">
-        <v>30.54097929390817</v>
+        <v>30.91989741795621</v>
       </c>
       <c r="O7" t="n">
-        <v>5.526389354172231</v>
+        <v>5.560566285726321</v>
       </c>
       <c r="P7" t="n">
-        <v>382.6676297850629</v>
+        <v>382.8736703518096</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19296,7 +19496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H418"/>
+  <dimension ref="A1:H423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36839,6 +37039,216 @@
         </is>
       </c>
     </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>-36.04784337744961,174.56478901981558</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>-36.04811256677757,174.56563996074752</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>-36.048301830454896,174.5665036070357</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>-36.04838256792286,174.56738021689299</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>-36.04843757018087,174.5682581777292</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>-36.04839925133582,174.5691437031436</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>-36.0478586291702,174.56478559316892</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>-36.04812925351151,174.56563632673993</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>-36.04830406141232,174.56650321625793</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>-36.04838112878265,174.5673803322328</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>-36.04844937074624,174.5682586896842</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>-36.048398802381215,174.5691436545922</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:05+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>-36.0478586291702,174.56478559316892</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>-36.04812925351151,174.56563632673993</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>-36.04830299055275,174.56650340383126</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>-36.048378250502246,174.56738056291246</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>-36.04845270373035,174.5682588342822</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>-36.04839386388049,174.56914312052712</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>-36.04787193008923,174.56478260481325</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>-36.04812818840083,174.56563655869792</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>-36.04830477531868,174.56650309120903</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>-36.048394710668305,174.56737924371302</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>-36.048458378811375,174.56825908048967</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>-36.04840149610888,174.56914394590046</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>-36.04787902391268,174.5647810110232</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>-36.04813777439687,174.56563447107595</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>-36.04830129502512,174.5665037008224</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>-36.048389583731336,174.56737965461124</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>-36.04845810856943,174.5682590687655</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>-36.04839826363568,174.56914359633058</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0111/nzd0111.xlsx
+++ b/data/nzd0111/nzd0111.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H423"/>
+  <dimension ref="A1:H428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13120,6 +13120,156 @@
         <v>374.88</v>
       </c>
       <c r="H423" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:04:43+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>394.05</v>
+      </c>
+      <c r="C424" t="n">
+        <v>381.77</v>
+      </c>
+      <c r="D424" t="n">
+        <v>378.11</v>
+      </c>
+      <c r="E424" t="n">
+        <v>378.21</v>
+      </c>
+      <c r="F424" t="n">
+        <v>373.54</v>
+      </c>
+      <c r="G424" t="n">
+        <v>373.21</v>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>396.82</v>
+      </c>
+      <c r="C425" t="n">
+        <v>380.74</v>
+      </c>
+      <c r="D425" t="n">
+        <v>377.17</v>
+      </c>
+      <c r="E425" t="n">
+        <v>379.23</v>
+      </c>
+      <c r="F425" t="n">
+        <v>373.54</v>
+      </c>
+      <c r="G425" t="n">
+        <v>375.25</v>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>399.27</v>
+      </c>
+      <c r="C426" t="n">
+        <v>380.5</v>
+      </c>
+      <c r="D426" t="n">
+        <v>376.78</v>
+      </c>
+      <c r="E426" t="n">
+        <v>379.89</v>
+      </c>
+      <c r="F426" t="n">
+        <v>374.83</v>
+      </c>
+      <c r="G426" t="n">
+        <v>377.39</v>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>399.85</v>
+      </c>
+      <c r="C427" t="n">
+        <v>381.44</v>
+      </c>
+      <c r="D427" t="n">
+        <v>377.62</v>
+      </c>
+      <c r="E427" t="n">
+        <v>379.18</v>
+      </c>
+      <c r="F427" t="n">
+        <v>374.8</v>
+      </c>
+      <c r="G427" t="n">
+        <v>377.17</v>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>400.63</v>
+      </c>
+      <c r="C428" t="n">
+        <v>380.36</v>
+      </c>
+      <c r="D428" t="n">
+        <v>376.73</v>
+      </c>
+      <c r="E428" t="n">
+        <v>379.32</v>
+      </c>
+      <c r="F428" t="n">
+        <v>374.61</v>
+      </c>
+      <c r="G428" t="n">
+        <v>377.39</v>
+      </c>
+      <c r="H428" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13136,7 +13286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B574"/>
+  <dimension ref="A1:B579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18879,6 +19029,56 @@
       </c>
       <c r="B574" t="n">
         <v>-0.15</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>-0.74</v>
       </c>
     </row>
   </sheetData>
@@ -19047,28 +19247,28 @@
         <v>0.053</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1109920853137151</v>
+        <v>0.1086407139522728</v>
       </c>
       <c r="J2" t="n">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="K2" t="n">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02154107547049966</v>
+        <v>0.02119028890571162</v>
       </c>
       <c r="M2" t="n">
-        <v>3.950691101398388</v>
+        <v>3.925271470808643</v>
       </c>
       <c r="N2" t="n">
-        <v>31.11352007400109</v>
+        <v>30.82617160946015</v>
       </c>
       <c r="O2" t="n">
-        <v>5.577949450649503</v>
+        <v>5.552132167866697</v>
       </c>
       <c r="P2" t="n">
-        <v>396.1288726933631</v>
+        <v>396.1531318280266</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19125,28 +19325,28 @@
         <v>0.0517</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1516225914475232</v>
+        <v>0.1365722796710327</v>
       </c>
       <c r="J3" t="n">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="K3" t="n">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05536217295712675</v>
+        <v>0.04574289124905506</v>
       </c>
       <c r="M3" t="n">
-        <v>3.415200960572585</v>
+        <v>3.442913913373792</v>
       </c>
       <c r="N3" t="n">
-        <v>21.90880999907227</v>
+        <v>22.09990010990077</v>
       </c>
       <c r="O3" t="n">
-        <v>4.680684778862199</v>
+        <v>4.701053085203438</v>
       </c>
       <c r="P3" t="n">
-        <v>383.1844186344237</v>
+        <v>383.3393151462245</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19203,28 +19403,28 @@
         <v>0.0497</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1828704773812529</v>
+        <v>0.1605260305361629</v>
       </c>
       <c r="J4" t="n">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="K4" t="n">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08137507950269873</v>
+        <v>0.06285795550234263</v>
       </c>
       <c r="M4" t="n">
-        <v>3.48148118357086</v>
+        <v>3.539567437046838</v>
       </c>
       <c r="N4" t="n">
-        <v>21.08495839134615</v>
+        <v>21.82023912209207</v>
       </c>
       <c r="O4" t="n">
-        <v>4.591836058849026</v>
+        <v>4.671213881004816</v>
       </c>
       <c r="P4" t="n">
-        <v>381.7128564204488</v>
+        <v>381.9428202196164</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19281,28 +19481,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04600223358216609</v>
+        <v>0.02691265158850729</v>
       </c>
       <c r="J5" t="n">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="K5" t="n">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005804575934685752</v>
+        <v>0.001980968516337778</v>
       </c>
       <c r="M5" t="n">
-        <v>3.487944943437795</v>
+        <v>3.527458521651966</v>
       </c>
       <c r="N5" t="n">
-        <v>20.24407113933147</v>
+        <v>20.72514742535674</v>
       </c>
       <c r="O5" t="n">
-        <v>4.499341189477796</v>
+        <v>4.552488047799438</v>
       </c>
       <c r="P5" t="n">
-        <v>385.9032627191947</v>
+        <v>386.0997154601096</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19359,28 +19559,28 @@
         <v>0.0648</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0250358000842579</v>
+        <v>-0.03927540046860437</v>
       </c>
       <c r="J6" t="n">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="K6" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001323567221282462</v>
+        <v>0.00329469183289588</v>
       </c>
       <c r="M6" t="n">
-        <v>4.053688506839947</v>
+        <v>4.068240793120789</v>
       </c>
       <c r="N6" t="n">
-        <v>26.26825562879246</v>
+        <v>26.35872482224415</v>
       </c>
       <c r="O6" t="n">
-        <v>5.125256640285681</v>
+        <v>5.134074875013428</v>
       </c>
       <c r="P6" t="n">
-        <v>380.8518785081047</v>
+        <v>380.9990642397951</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19437,28 +19637,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01003365269954293</v>
+        <v>-0.02572909796120841</v>
       </c>
       <c r="J7" t="n">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="K7" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001808135766265817</v>
+        <v>0.001202091274133288</v>
       </c>
       <c r="M7" t="n">
-        <v>4.552958279513748</v>
+        <v>4.577525456013781</v>
       </c>
       <c r="N7" t="n">
-        <v>30.91989741795621</v>
+        <v>31.06851396819445</v>
       </c>
       <c r="O7" t="n">
-        <v>5.560566285726321</v>
+        <v>5.573913702973383</v>
       </c>
       <c r="P7" t="n">
-        <v>382.8736703518096</v>
+        <v>383.0358837445018</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19496,7 +19696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H423"/>
+  <dimension ref="A1:H428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37249,6 +37449,216 @@
         </is>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:04:43+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>-36.04790757655185,174.56477459601552</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>-36.04815392857528,174.5656309530453</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>-36.04831557315254,174.56650119984414</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>-36.04840307567072,174.56737857330003</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>-36.04846531502153,174.56825938141</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>-36.0484132587197,174.56914521794687</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>-36.04788301418836,174.56478011451614</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>-36.04816307077512,174.5656289620713</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>-36.04832396155237,174.566499730519</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>-36.04839390115195,174.5673793085917</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>-36.04846531502153,174.56825938141</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>-36.04839494137156,174.5691432370504</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>-36.04786128935402,174.56478499549786</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>-36.04816520099642,174.56562849815498</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>-36.04832744184591,174.56649912090532</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>-36.04838796469861,174.5673797843686</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>-36.04845369461752,174.5682588772708</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>-36.04837572611408,174.56914115905232</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>-36.047856146331966,174.56478615099522</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>-36.04815685762961,174.56563031516046</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>-36.04831994582906,174.56650043391937</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>-36.04839435088326,174.56737927254798</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>-36.048453964859476,174.56825888899496</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>-36.048377701514376,174.56914137267825</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>-36.04784922985404,174.56478770493968</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>-36.04816644362554,174.5656282275371</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>-36.048327888037385,174.5664990427497</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>-36.04839309163559,174.56737937347037</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>-36.04845567639185,174.568258963248</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>-36.04837572611408,174.56914115905232</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
